--- a/data/exports/net_addition_merged.xlsx
+++ b/data/exports/net_addition_merged.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,38 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J576"/>
+  <dimension ref="A1:J589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="n">
+      <c r="A1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="D1" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="E1" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="F1" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="G1" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="H1" t="n">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="I1" t="n">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="J1" t="n">
         <v>9</v>
       </c>
     </row>
@@ -17147,17 +17135,17 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Bahu SO</t>
+          <t>Assaudha SO</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C491" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D491" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E491" t="n">
         <v>0</v>
@@ -17181,26 +17169,26 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Beri SO</t>
+          <t>Badli SO Jhajjar</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C492" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D492" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="E492" t="n">
         <v>0</v>
       </c>
       <c r="F492" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G492" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -17215,26 +17203,26 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Court Complex Jhajjar SO</t>
+          <t>Bahadurgarh HO</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C493" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D493" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E493" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F493" t="n">
         <v>0</v>
       </c>
       <c r="G493" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -17249,26 +17237,26 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Dhakla SO</t>
+          <t>Bahadurgarh Mandi SO</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C494" t="n">
         <v>2</v>
       </c>
       <c r="D494" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E494" t="n">
         <v>0</v>
       </c>
       <c r="F494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H494" t="n">
         <v>0</v>
@@ -17283,26 +17271,26 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Dighal SO</t>
+          <t>Bahadurgarh Sector 6 SO</t>
         </is>
       </c>
       <c r="B495" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C495" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F495" t="n">
         <v>0</v>
       </c>
       <c r="G495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -17317,17 +17305,17 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Dubaldhan SO</t>
+          <t>Charra SO</t>
         </is>
       </c>
       <c r="B496" t="n">
         <v>7</v>
       </c>
       <c r="C496" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D496" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E496" t="n">
         <v>0</v>
@@ -17351,17 +17339,17 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Dujana SO</t>
+          <t>Hassangarh SO</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C497" t="n">
         <v>3</v>
       </c>
       <c r="D497" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E497" t="n">
         <v>0</v>
@@ -17385,51 +17373,51 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Jhajjar SO</t>
+          <t>Main Bazar Bahadurgarh  SO</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C498" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D498" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E498" t="n">
         <v>1</v>
       </c>
       <c r="F498" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G498" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H498" t="n">
         <v>0</v>
       </c>
       <c r="I498" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J498" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Machrauli SO</t>
+          <t>Mandothi SO</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D499" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E499" t="n">
         <v>0</v>
@@ -17453,26 +17441,26 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Matanhail SO</t>
+          <t>Sampla SO</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C500" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D500" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E500" t="n">
         <v>0</v>
       </c>
       <c r="F500" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G500" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -17487,26 +17475,26 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Mehem SO</t>
+          <t>Total:</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="C501" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="D501" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E501" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F501" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G501" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -17520,258 +17508,258 @@
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
-        <is>
-          <t>MET Dadri Toe S.O</t>
-        </is>
-      </c>
-      <c r="B502" t="n">
-        <v>0</v>
-      </c>
-      <c r="C502" t="n">
-        <v>0</v>
-      </c>
-      <c r="D502" t="n">
-        <v>0</v>
-      </c>
-      <c r="E502" t="n">
-        <v>0</v>
-      </c>
-      <c r="F502" t="n">
-        <v>0</v>
-      </c>
-      <c r="G502" t="n">
-        <v>0</v>
-      </c>
-      <c r="H502" t="n">
-        <v>0</v>
-      </c>
-      <c r="I502" t="n">
-        <v>0</v>
-      </c>
-      <c r="J502" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>Nehru College Jhajjar SO</t>
-        </is>
-      </c>
-      <c r="B503" t="n">
-        <v>26</v>
-      </c>
-      <c r="C503" t="n">
-        <v>3</v>
-      </c>
-      <c r="D503" t="n">
-        <v>23</v>
-      </c>
-      <c r="E503" t="n">
-        <v>0</v>
-      </c>
-      <c r="F503" t="n">
-        <v>0</v>
-      </c>
-      <c r="G503" t="n">
-        <v>0</v>
-      </c>
-      <c r="H503" t="n">
-        <v>0</v>
-      </c>
-      <c r="I503" t="n">
-        <v>0</v>
-      </c>
-      <c r="J503" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>Power Plant Jharli SO</t>
-        </is>
-      </c>
-      <c r="B504" t="n">
-        <v>0</v>
-      </c>
-      <c r="C504" t="n">
-        <v>0</v>
-      </c>
-      <c r="D504" t="n">
-        <v>0</v>
-      </c>
-      <c r="E504" t="n">
-        <v>0</v>
-      </c>
-      <c r="F504" t="n">
-        <v>0</v>
-      </c>
-      <c r="G504" t="n">
-        <v>0</v>
-      </c>
-      <c r="H504" t="n">
-        <v>0</v>
-      </c>
-      <c r="I504" t="n">
-        <v>0</v>
-      </c>
-      <c r="J504" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>Sahlawas SO</t>
-        </is>
-      </c>
-      <c r="B505" t="n">
-        <v>8</v>
-      </c>
-      <c r="C505" t="n">
-        <v>12</v>
-      </c>
-      <c r="D505" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E505" t="n">
-        <v>0</v>
-      </c>
-      <c r="F505" t="n">
-        <v>0</v>
-      </c>
-      <c r="G505" t="n">
-        <v>0</v>
-      </c>
-      <c r="H505" t="n">
-        <v>0</v>
-      </c>
-      <c r="I505" t="n">
-        <v>0</v>
-      </c>
-      <c r="J505" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>Total:</t>
-        </is>
-      </c>
-      <c r="B506" t="n">
-        <v>160</v>
-      </c>
-      <c r="C506" t="n">
-        <v>71</v>
-      </c>
-      <c r="D506" t="n">
-        <v>89</v>
-      </c>
-      <c r="E506" t="n">
-        <v>2</v>
-      </c>
-      <c r="F506" t="n">
-        <v>3</v>
-      </c>
-      <c r="G506" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H506" t="n">
-        <v>0</v>
-      </c>
-      <c r="I506" t="n">
-        <v>1</v>
-      </c>
-      <c r="J506" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Product Wise A/C Report
 </t>
         </is>
       </c>
-      <c r="B507" t="inlineStr"/>
-      <c r="C507" t="inlineStr"/>
-      <c r="D507" t="inlineStr"/>
-      <c r="E507" t="inlineStr"/>
-      <c r="F507" t="inlineStr"/>
-      <c r="G507" t="inlineStr"/>
-      <c r="H507" t="inlineStr"/>
-      <c r="I507" t="inlineStr"/>
-      <c r="J507" t="inlineStr"/>
+      <c r="B502" t="inlineStr"/>
+      <c r="C502" t="inlineStr"/>
+      <c r="D502" t="inlineStr"/>
+      <c r="E502" t="inlineStr"/>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr"/>
+      <c r="I502" t="inlineStr"/>
+      <c r="J502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>A/c Opened</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>A/c Closed</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Cert Issued</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Cert Discharged</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>A/c Opened</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>A/c Closed</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Bahu SO</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>14</v>
+      </c>
+      <c r="C504" t="n">
+        <v>3</v>
+      </c>
+      <c r="D504" t="n">
+        <v>11</v>
+      </c>
+      <c r="E504" t="n">
+        <v>0</v>
+      </c>
+      <c r="F504" t="n">
+        <v>0</v>
+      </c>
+      <c r="G504" t="n">
+        <v>0</v>
+      </c>
+      <c r="H504" t="n">
+        <v>0</v>
+      </c>
+      <c r="I504" t="n">
+        <v>0</v>
+      </c>
+      <c r="J504" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Beri SO</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>14</v>
+      </c>
+      <c r="C505" t="n">
+        <v>8</v>
+      </c>
+      <c r="D505" t="n">
+        <v>6</v>
+      </c>
+      <c r="E505" t="n">
+        <v>0</v>
+      </c>
+      <c r="F505" t="n">
+        <v>1</v>
+      </c>
+      <c r="G505" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H505" t="n">
+        <v>0</v>
+      </c>
+      <c r="I505" t="n">
+        <v>0</v>
+      </c>
+      <c r="J505" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Court Complex Jhajjar SO</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>2</v>
+      </c>
+      <c r="C506" t="n">
+        <v>2</v>
+      </c>
+      <c r="D506" t="n">
+        <v>0</v>
+      </c>
+      <c r="E506" t="n">
+        <v>0</v>
+      </c>
+      <c r="F506" t="n">
+        <v>0</v>
+      </c>
+      <c r="G506" t="n">
+        <v>0</v>
+      </c>
+      <c r="H506" t="n">
+        <v>0</v>
+      </c>
+      <c r="I506" t="n">
+        <v>0</v>
+      </c>
+      <c r="J506" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Dhakla SO</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>14</v>
+      </c>
+      <c r="C507" t="n">
+        <v>2</v>
+      </c>
+      <c r="D507" t="n">
+        <v>12</v>
+      </c>
+      <c r="E507" t="n">
+        <v>0</v>
+      </c>
+      <c r="F507" t="n">
+        <v>0</v>
+      </c>
+      <c r="G507" t="n">
+        <v>0</v>
+      </c>
+      <c r="H507" t="n">
+        <v>0</v>
+      </c>
+      <c r="I507" t="n">
+        <v>0</v>
+      </c>
+      <c r="J507" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>A/c Opened</t>
-        </is>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>A/c Closed</t>
-        </is>
-      </c>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E508" t="inlineStr">
-        <is>
-          <t>Cert Issued</t>
-        </is>
-      </c>
-      <c r="F508" t="inlineStr">
-        <is>
-          <t>Cert Discharged</t>
-        </is>
-      </c>
-      <c r="G508" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="H508" t="inlineStr">
-        <is>
-          <t>A/c Opened</t>
-        </is>
-      </c>
-      <c r="I508" t="inlineStr">
-        <is>
-          <t>A/c Closed</t>
-        </is>
-      </c>
-      <c r="J508" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
+          <t>Dighal SO</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>6</v>
+      </c>
+      <c r="C508" t="n">
+        <v>6</v>
+      </c>
+      <c r="D508" t="n">
+        <v>0</v>
+      </c>
+      <c r="E508" t="n">
+        <v>0</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0</v>
+      </c>
+      <c r="G508" t="n">
+        <v>0</v>
+      </c>
+      <c r="H508" t="n">
+        <v>0</v>
+      </c>
+      <c r="I508" t="n">
+        <v>0</v>
+      </c>
+      <c r="J508" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Anwal SO</t>
+          <t>Dubaldhan SO</t>
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C509" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D509" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E509" t="n">
         <v>0</v>
@@ -17795,17 +17783,17 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Asthal Bohar SO</t>
+          <t>Dujana SO</t>
         </is>
       </c>
       <c r="B510" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C510" t="n">
+        <v>3</v>
+      </c>
+      <c r="D510" t="n">
         <v>5</v>
-      </c>
-      <c r="D510" t="n">
-        <v>27</v>
       </c>
       <c r="E510" t="n">
         <v>0</v>
@@ -17829,23 +17817,23 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Bhalaut SO</t>
+          <t>Jhajjar SO</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C511" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D511" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E511" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F511" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G511" t="n">
         <v>0</v>
@@ -17854,26 +17842,26 @@
         <v>0</v>
       </c>
       <c r="I511" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J511" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Bus Stand</t>
+          <t>Machrauli SO</t>
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C512" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D512" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E512" t="n">
         <v>0</v>
@@ -17897,7 +17885,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>DLF Colony Rohtak SO</t>
+          <t>Matanhail SO</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -17931,23 +17919,23 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Gandhi Camp SO</t>
+          <t>Mehem SO</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C514" t="n">
         <v>6</v>
       </c>
       <c r="D514" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E514" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F514" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G514" t="n">
         <v>0</v>
@@ -17965,7 +17953,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Gohana Road SO Rohtak</t>
+          <t>MET Dadri Toe S.O</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -17999,17 +17987,17 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Indra Colony Rohtak S.O</t>
+          <t>Nehru College Jhajjar SO</t>
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C516" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D516" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E516" t="n">
         <v>0</v>
@@ -18033,26 +18021,26 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Janta Colony Rohtak SO</t>
+          <t>Power Plant Jharli SO</t>
         </is>
       </c>
       <c r="B517" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C517" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D517" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E517" t="n">
         <v>0</v>
       </c>
       <c r="F517" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G517" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -18067,17 +18055,17 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Jhajjar Road Rohtak SO</t>
+          <t>Sahlawas SO</t>
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C518" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D518" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="E518" t="n">
         <v>0</v>
@@ -18101,665 +18089,665 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Kahnaur SO</t>
+          <t>Total:</t>
         </is>
       </c>
       <c r="B519" t="n">
-        <v>7</v>
+        <v>160</v>
       </c>
       <c r="C519" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="D519" t="n">
+        <v>89</v>
+      </c>
+      <c r="E519" t="n">
+        <v>2</v>
+      </c>
+      <c r="F519" t="n">
         <v>3</v>
       </c>
-      <c r="E519" t="n">
-        <v>0</v>
-      </c>
-      <c r="F519" t="n">
-        <v>0</v>
-      </c>
       <c r="G519" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
       </c>
       <c r="I519" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J519" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
-        <is>
-          <t>Kalanaur SO Rohtak</t>
-        </is>
-      </c>
-      <c r="B520" t="n">
-        <v>9</v>
-      </c>
-      <c r="C520" t="n">
-        <v>1</v>
-      </c>
-      <c r="D520" t="n">
-        <v>8</v>
-      </c>
-      <c r="E520" t="n">
-        <v>0</v>
-      </c>
-      <c r="F520" t="n">
-        <v>0</v>
-      </c>
-      <c r="G520" t="n">
-        <v>0</v>
-      </c>
-      <c r="H520" t="n">
-        <v>0</v>
-      </c>
-      <c r="I520" t="n">
-        <v>0</v>
-      </c>
-      <c r="J520" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>Kansala SO</t>
-        </is>
-      </c>
-      <c r="B521" t="n">
-        <v>11</v>
-      </c>
-      <c r="C521" t="n">
-        <v>19</v>
-      </c>
-      <c r="D521" t="n">
-        <v>-8</v>
-      </c>
-      <c r="E521" t="n">
-        <v>0</v>
-      </c>
-      <c r="F521" t="n">
-        <v>0</v>
-      </c>
-      <c r="G521" t="n">
-        <v>0</v>
-      </c>
-      <c r="H521" t="n">
-        <v>0</v>
-      </c>
-      <c r="I521" t="n">
-        <v>0</v>
-      </c>
-      <c r="J521" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>Lakhan Majra SO</t>
-        </is>
-      </c>
-      <c r="B522" t="n">
-        <v>13</v>
-      </c>
-      <c r="C522" t="n">
-        <v>3</v>
-      </c>
-      <c r="D522" t="n">
-        <v>10</v>
-      </c>
-      <c r="E522" t="n">
-        <v>0</v>
-      </c>
-      <c r="F522" t="n">
-        <v>0</v>
-      </c>
-      <c r="G522" t="n">
-        <v>0</v>
-      </c>
-      <c r="H522" t="n">
-        <v>0</v>
-      </c>
-      <c r="I522" t="n">
-        <v>1</v>
-      </c>
-      <c r="J522" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>Madina SO</t>
-        </is>
-      </c>
-      <c r="B523" t="n">
-        <v>56</v>
-      </c>
-      <c r="C523" t="n">
-        <v>7</v>
-      </c>
-      <c r="D523" t="n">
-        <v>49</v>
-      </c>
-      <c r="E523" t="n">
-        <v>0</v>
-      </c>
-      <c r="F523" t="n">
-        <v>0</v>
-      </c>
-      <c r="G523" t="n">
-        <v>0</v>
-      </c>
-      <c r="H523" t="n">
-        <v>0</v>
-      </c>
-      <c r="I523" t="n">
-        <v>0</v>
-      </c>
-      <c r="J523" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>MD University Rohtak SO</t>
-        </is>
-      </c>
-      <c r="B524" t="n">
-        <v>0</v>
-      </c>
-      <c r="C524" t="n">
-        <v>0</v>
-      </c>
-      <c r="D524" t="n">
-        <v>0</v>
-      </c>
-      <c r="E524" t="n">
-        <v>0</v>
-      </c>
-      <c r="F524" t="n">
-        <v>0</v>
-      </c>
-      <c r="G524" t="n">
-        <v>0</v>
-      </c>
-      <c r="H524" t="n">
-        <v>0</v>
-      </c>
-      <c r="I524" t="n">
-        <v>0</v>
-      </c>
-      <c r="J524" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>Medical College SO Rohtak</t>
-        </is>
-      </c>
-      <c r="B525" t="n">
-        <v>0</v>
-      </c>
-      <c r="C525" t="n">
-        <v>0</v>
-      </c>
-      <c r="D525" t="n">
-        <v>0</v>
-      </c>
-      <c r="E525" t="n">
-        <v>0</v>
-      </c>
-      <c r="F525" t="n">
-        <v>0</v>
-      </c>
-      <c r="G525" t="n">
-        <v>0</v>
-      </c>
-      <c r="H525" t="n">
-        <v>0</v>
-      </c>
-      <c r="I525" t="n">
-        <v>0</v>
-      </c>
-      <c r="J525" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>Model Town SO Rohtak</t>
-        </is>
-      </c>
-      <c r="B526" t="n">
-        <v>5</v>
-      </c>
-      <c r="C526" t="n">
-        <v>3</v>
-      </c>
-      <c r="D526" t="n">
-        <v>2</v>
-      </c>
-      <c r="E526" t="n">
-        <v>3</v>
-      </c>
-      <c r="F526" t="n">
-        <v>2</v>
-      </c>
-      <c r="G526" t="n">
-        <v>1</v>
-      </c>
-      <c r="H526" t="n">
-        <v>0</v>
-      </c>
-      <c r="I526" t="n">
-        <v>0</v>
-      </c>
-      <c r="J526" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>Mokhra SO</t>
-        </is>
-      </c>
-      <c r="B527" t="n">
-        <v>1</v>
-      </c>
-      <c r="C527" t="n">
-        <v>3</v>
-      </c>
-      <c r="D527" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E527" t="n">
-        <v>0</v>
-      </c>
-      <c r="F527" t="n">
-        <v>0</v>
-      </c>
-      <c r="G527" t="n">
-        <v>0</v>
-      </c>
-      <c r="H527" t="n">
-        <v>0</v>
-      </c>
-      <c r="I527" t="n">
-        <v>0</v>
-      </c>
-      <c r="J527" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>Nindana SO</t>
-        </is>
-      </c>
-      <c r="B528" t="n">
-        <v>2</v>
-      </c>
-      <c r="C528" t="n">
-        <v>0</v>
-      </c>
-      <c r="D528" t="n">
-        <v>2</v>
-      </c>
-      <c r="E528" t="n">
-        <v>0</v>
-      </c>
-      <c r="F528" t="n">
-        <v>0</v>
-      </c>
-      <c r="G528" t="n">
-        <v>0</v>
-      </c>
-      <c r="H528" t="n">
-        <v>0</v>
-      </c>
-      <c r="I528" t="n">
-        <v>0</v>
-      </c>
-      <c r="J528" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>Police Training Center Sunaria SO</t>
-        </is>
-      </c>
-      <c r="B529" t="n">
-        <v>12</v>
-      </c>
-      <c r="C529" t="n">
-        <v>2</v>
-      </c>
-      <c r="D529" t="n">
-        <v>10</v>
-      </c>
-      <c r="E529" t="n">
-        <v>0</v>
-      </c>
-      <c r="F529" t="n">
-        <v>0</v>
-      </c>
-      <c r="G529" t="n">
-        <v>0</v>
-      </c>
-      <c r="H529" t="n">
-        <v>0</v>
-      </c>
-      <c r="I529" t="n">
-        <v>0</v>
-      </c>
-      <c r="J529" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>Rohtak HO</t>
-        </is>
-      </c>
-      <c r="B530" t="n">
-        <v>18</v>
-      </c>
-      <c r="C530" t="n">
-        <v>13</v>
-      </c>
-      <c r="D530" t="n">
-        <v>5</v>
-      </c>
-      <c r="E530" t="n">
-        <v>0</v>
-      </c>
-      <c r="F530" t="n">
-        <v>3</v>
-      </c>
-      <c r="G530" t="n">
-        <v>-3</v>
-      </c>
-      <c r="H530" t="n">
-        <v>0</v>
-      </c>
-      <c r="I530" t="n">
-        <v>0</v>
-      </c>
-      <c r="J530" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>Rohtak Sector I SO</t>
-        </is>
-      </c>
-      <c r="B531" t="n">
-        <v>0</v>
-      </c>
-      <c r="C531" t="n">
-        <v>0</v>
-      </c>
-      <c r="D531" t="n">
-        <v>0</v>
-      </c>
-      <c r="E531" t="n">
-        <v>0</v>
-      </c>
-      <c r="F531" t="n">
-        <v>0</v>
-      </c>
-      <c r="G531" t="n">
-        <v>0</v>
-      </c>
-      <c r="H531" t="n">
-        <v>0</v>
-      </c>
-      <c r="I531" t="n">
-        <v>0</v>
-      </c>
-      <c r="J531" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>Rohtak Town SO</t>
-        </is>
-      </c>
-      <c r="B532" t="n">
-        <v>0</v>
-      </c>
-      <c r="C532" t="n">
-        <v>0</v>
-      </c>
-      <c r="D532" t="n">
-        <v>0</v>
-      </c>
-      <c r="E532" t="n">
-        <v>0</v>
-      </c>
-      <c r="F532" t="n">
-        <v>0</v>
-      </c>
-      <c r="G532" t="n">
-        <v>0</v>
-      </c>
-      <c r="H532" t="n">
-        <v>0</v>
-      </c>
-      <c r="I532" t="n">
-        <v>0</v>
-      </c>
-      <c r="J532" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>Sanghi SO</t>
-        </is>
-      </c>
-      <c r="B533" t="n">
-        <v>12</v>
-      </c>
-      <c r="C533" t="n">
-        <v>2</v>
-      </c>
-      <c r="D533" t="n">
-        <v>10</v>
-      </c>
-      <c r="E533" t="n">
-        <v>0</v>
-      </c>
-      <c r="F533" t="n">
-        <v>0</v>
-      </c>
-      <c r="G533" t="n">
-        <v>0</v>
-      </c>
-      <c r="H533" t="n">
-        <v>0</v>
-      </c>
-      <c r="I533" t="n">
-        <v>0</v>
-      </c>
-      <c r="J533" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>Shivaji Colony SO</t>
-        </is>
-      </c>
-      <c r="B534" t="n">
-        <v>0</v>
-      </c>
-      <c r="C534" t="n">
-        <v>0</v>
-      </c>
-      <c r="D534" t="n">
-        <v>0</v>
-      </c>
-      <c r="E534" t="n">
-        <v>0</v>
-      </c>
-      <c r="F534" t="n">
-        <v>0</v>
-      </c>
-      <c r="G534" t="n">
-        <v>0</v>
-      </c>
-      <c r="H534" t="n">
-        <v>0</v>
-      </c>
-      <c r="I534" t="n">
-        <v>0</v>
-      </c>
-      <c r="J534" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>Total:</t>
-        </is>
-      </c>
-      <c r="B535" t="n">
-        <v>196</v>
-      </c>
-      <c r="C535" t="n">
-        <v>73</v>
-      </c>
-      <c r="D535" t="n">
-        <v>123</v>
-      </c>
-      <c r="E535" t="n">
-        <v>3</v>
-      </c>
-      <c r="F535" t="n">
-        <v>8</v>
-      </c>
-      <c r="G535" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H535" t="n">
-        <v>0</v>
-      </c>
-      <c r="I535" t="n">
-        <v>1</v>
-      </c>
-      <c r="J535" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Product Wise A/C Report
 </t>
         </is>
       </c>
-      <c r="B536" t="inlineStr"/>
-      <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr"/>
-      <c r="F536" t="inlineStr"/>
-      <c r="G536" t="inlineStr"/>
-      <c r="H536" t="inlineStr"/>
-      <c r="I536" t="inlineStr"/>
-      <c r="J536" t="inlineStr"/>
+      <c r="B520" t="inlineStr"/>
+      <c r="C520" t="inlineStr"/>
+      <c r="D520" t="inlineStr"/>
+      <c r="E520" t="inlineStr"/>
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="inlineStr"/>
+      <c r="H520" t="inlineStr"/>
+      <c r="I520" t="inlineStr"/>
+      <c r="J520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>A/c Opened</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>A/c Closed</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Cert Issued</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Cert Discharged</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>A/c Opened</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>A/c Closed</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Anwal SO</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>0</v>
+      </c>
+      <c r="C522" t="n">
+        <v>0</v>
+      </c>
+      <c r="D522" t="n">
+        <v>0</v>
+      </c>
+      <c r="E522" t="n">
+        <v>0</v>
+      </c>
+      <c r="F522" t="n">
+        <v>0</v>
+      </c>
+      <c r="G522" t="n">
+        <v>0</v>
+      </c>
+      <c r="H522" t="n">
+        <v>0</v>
+      </c>
+      <c r="I522" t="n">
+        <v>0</v>
+      </c>
+      <c r="J522" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Asthal Bohar SO</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>32</v>
+      </c>
+      <c r="C523" t="n">
+        <v>5</v>
+      </c>
+      <c r="D523" t="n">
+        <v>27</v>
+      </c>
+      <c r="E523" t="n">
+        <v>0</v>
+      </c>
+      <c r="F523" t="n">
+        <v>0</v>
+      </c>
+      <c r="G523" t="n">
+        <v>0</v>
+      </c>
+      <c r="H523" t="n">
+        <v>0</v>
+      </c>
+      <c r="I523" t="n">
+        <v>0</v>
+      </c>
+      <c r="J523" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Bhalaut SO</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>11</v>
+      </c>
+      <c r="C524" t="n">
+        <v>1</v>
+      </c>
+      <c r="D524" t="n">
+        <v>10</v>
+      </c>
+      <c r="E524" t="n">
+        <v>0</v>
+      </c>
+      <c r="F524" t="n">
+        <v>0</v>
+      </c>
+      <c r="G524" t="n">
+        <v>0</v>
+      </c>
+      <c r="H524" t="n">
+        <v>0</v>
+      </c>
+      <c r="I524" t="n">
+        <v>0</v>
+      </c>
+      <c r="J524" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Bus Stand</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>0</v>
+      </c>
+      <c r="C525" t="n">
+        <v>0</v>
+      </c>
+      <c r="D525" t="n">
+        <v>0</v>
+      </c>
+      <c r="E525" t="n">
+        <v>0</v>
+      </c>
+      <c r="F525" t="n">
+        <v>0</v>
+      </c>
+      <c r="G525" t="n">
+        <v>0</v>
+      </c>
+      <c r="H525" t="n">
+        <v>0</v>
+      </c>
+      <c r="I525" t="n">
+        <v>0</v>
+      </c>
+      <c r="J525" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>DLF Colony Rohtak SO</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>0</v>
+      </c>
+      <c r="C526" t="n">
+        <v>0</v>
+      </c>
+      <c r="D526" t="n">
+        <v>0</v>
+      </c>
+      <c r="E526" t="n">
+        <v>0</v>
+      </c>
+      <c r="F526" t="n">
+        <v>0</v>
+      </c>
+      <c r="G526" t="n">
+        <v>0</v>
+      </c>
+      <c r="H526" t="n">
+        <v>0</v>
+      </c>
+      <c r="I526" t="n">
+        <v>0</v>
+      </c>
+      <c r="J526" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Gandhi Camp SO</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>2</v>
+      </c>
+      <c r="C527" t="n">
+        <v>6</v>
+      </c>
+      <c r="D527" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E527" t="n">
+        <v>0</v>
+      </c>
+      <c r="F527" t="n">
+        <v>0</v>
+      </c>
+      <c r="G527" t="n">
+        <v>0</v>
+      </c>
+      <c r="H527" t="n">
+        <v>0</v>
+      </c>
+      <c r="I527" t="n">
+        <v>0</v>
+      </c>
+      <c r="J527" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Gohana Road SO Rohtak</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>0</v>
+      </c>
+      <c r="C528" t="n">
+        <v>0</v>
+      </c>
+      <c r="D528" t="n">
+        <v>0</v>
+      </c>
+      <c r="E528" t="n">
+        <v>0</v>
+      </c>
+      <c r="F528" t="n">
+        <v>0</v>
+      </c>
+      <c r="G528" t="n">
+        <v>0</v>
+      </c>
+      <c r="H528" t="n">
+        <v>0</v>
+      </c>
+      <c r="I528" t="n">
+        <v>0</v>
+      </c>
+      <c r="J528" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Indra Colony Rohtak S.O</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>0</v>
+      </c>
+      <c r="C529" t="n">
+        <v>0</v>
+      </c>
+      <c r="D529" t="n">
+        <v>0</v>
+      </c>
+      <c r="E529" t="n">
+        <v>0</v>
+      </c>
+      <c r="F529" t="n">
+        <v>0</v>
+      </c>
+      <c r="G529" t="n">
+        <v>0</v>
+      </c>
+      <c r="H529" t="n">
+        <v>0</v>
+      </c>
+      <c r="I529" t="n">
+        <v>0</v>
+      </c>
+      <c r="J529" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Janta Colony Rohtak SO</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>5</v>
+      </c>
+      <c r="C530" t="n">
+        <v>4</v>
+      </c>
+      <c r="D530" t="n">
+        <v>1</v>
+      </c>
+      <c r="E530" t="n">
+        <v>0</v>
+      </c>
+      <c r="F530" t="n">
+        <v>3</v>
+      </c>
+      <c r="G530" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H530" t="n">
+        <v>0</v>
+      </c>
+      <c r="I530" t="n">
+        <v>0</v>
+      </c>
+      <c r="J530" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Jhajjar Road Rohtak SO</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>0</v>
+      </c>
+      <c r="C531" t="n">
+        <v>0</v>
+      </c>
+      <c r="D531" t="n">
+        <v>0</v>
+      </c>
+      <c r="E531" t="n">
+        <v>0</v>
+      </c>
+      <c r="F531" t="n">
+        <v>0</v>
+      </c>
+      <c r="G531" t="n">
+        <v>0</v>
+      </c>
+      <c r="H531" t="n">
+        <v>0</v>
+      </c>
+      <c r="I531" t="n">
+        <v>0</v>
+      </c>
+      <c r="J531" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Kahnaur SO</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>7</v>
+      </c>
+      <c r="C532" t="n">
+        <v>4</v>
+      </c>
+      <c r="D532" t="n">
+        <v>3</v>
+      </c>
+      <c r="E532" t="n">
+        <v>0</v>
+      </c>
+      <c r="F532" t="n">
+        <v>0</v>
+      </c>
+      <c r="G532" t="n">
+        <v>0</v>
+      </c>
+      <c r="H532" t="n">
+        <v>0</v>
+      </c>
+      <c r="I532" t="n">
+        <v>0</v>
+      </c>
+      <c r="J532" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Kalanaur SO Rohtak</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>9</v>
+      </c>
+      <c r="C533" t="n">
+        <v>1</v>
+      </c>
+      <c r="D533" t="n">
+        <v>8</v>
+      </c>
+      <c r="E533" t="n">
+        <v>0</v>
+      </c>
+      <c r="F533" t="n">
+        <v>0</v>
+      </c>
+      <c r="G533" t="n">
+        <v>0</v>
+      </c>
+      <c r="H533" t="n">
+        <v>0</v>
+      </c>
+      <c r="I533" t="n">
+        <v>0</v>
+      </c>
+      <c r="J533" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Kansala SO</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>11</v>
+      </c>
+      <c r="C534" t="n">
+        <v>19</v>
+      </c>
+      <c r="D534" t="n">
+        <v>-8</v>
+      </c>
+      <c r="E534" t="n">
+        <v>0</v>
+      </c>
+      <c r="F534" t="n">
+        <v>0</v>
+      </c>
+      <c r="G534" t="n">
+        <v>0</v>
+      </c>
+      <c r="H534" t="n">
+        <v>0</v>
+      </c>
+      <c r="I534" t="n">
+        <v>0</v>
+      </c>
+      <c r="J534" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Lakhan Majra SO</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>13</v>
+      </c>
+      <c r="C535" t="n">
+        <v>3</v>
+      </c>
+      <c r="D535" t="n">
+        <v>10</v>
+      </c>
+      <c r="E535" t="n">
+        <v>0</v>
+      </c>
+      <c r="F535" t="n">
+        <v>0</v>
+      </c>
+      <c r="G535" t="n">
+        <v>0</v>
+      </c>
+      <c r="H535" t="n">
+        <v>0</v>
+      </c>
+      <c r="I535" t="n">
+        <v>1</v>
+      </c>
+      <c r="J535" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Madina SO</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>56</v>
+      </c>
+      <c r="C536" t="n">
+        <v>7</v>
+      </c>
+      <c r="D536" t="n">
+        <v>49</v>
+      </c>
+      <c r="E536" t="n">
+        <v>0</v>
+      </c>
+      <c r="F536" t="n">
+        <v>0</v>
+      </c>
+      <c r="G536" t="n">
+        <v>0</v>
+      </c>
+      <c r="H536" t="n">
+        <v>0</v>
+      </c>
+      <c r="I536" t="n">
+        <v>0</v>
+      </c>
+      <c r="J536" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>A/c Opened</t>
-        </is>
-      </c>
-      <c r="C537" t="inlineStr">
-        <is>
-          <t>A/c Closed</t>
-        </is>
-      </c>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E537" t="inlineStr">
-        <is>
-          <t>Cert Issued</t>
-        </is>
-      </c>
-      <c r="F537" t="inlineStr">
-        <is>
-          <t>Cert Discharged</t>
-        </is>
-      </c>
-      <c r="G537" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="H537" t="inlineStr">
-        <is>
-          <t>A/c Opened</t>
-        </is>
-      </c>
-      <c r="I537" t="inlineStr">
-        <is>
-          <t>A/c Closed</t>
-        </is>
-      </c>
-      <c r="J537" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
+          <t>MD University Rohtak SO</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>0</v>
+      </c>
+      <c r="C537" t="n">
+        <v>0</v>
+      </c>
+      <c r="D537" t="n">
+        <v>0</v>
+      </c>
+      <c r="E537" t="n">
+        <v>0</v>
+      </c>
+      <c r="F537" t="n">
+        <v>0</v>
+      </c>
+      <c r="G537" t="n">
+        <v>0</v>
+      </c>
+      <c r="H537" t="n">
+        <v>0</v>
+      </c>
+      <c r="I537" t="n">
+        <v>0</v>
+      </c>
+      <c r="J537" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Baroda SO</t>
+          <t>Medical College SO Rohtak</t>
         </is>
       </c>
       <c r="B538" t="n">
         <v>0</v>
       </c>
       <c r="C538" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D538" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E538" t="n">
         <v>0</v>
@@ -18783,26 +18771,26 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Bhainswal Kalan SO</t>
+          <t>Model Town SO Rohtak</t>
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C539" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D539" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E539" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F539" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G539" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -18817,17 +18805,17 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Bus Stand Gohana SO</t>
+          <t>Mokhra SO</t>
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C540" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D540" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E540" t="n">
         <v>0</v>
@@ -18851,17 +18839,17 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Butana SO</t>
+          <t>Nindana SO</t>
         </is>
       </c>
       <c r="B541" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C541" t="n">
+        <v>0</v>
+      </c>
+      <c r="D541" t="n">
         <v>2</v>
-      </c>
-      <c r="D541" t="n">
-        <v>14</v>
       </c>
       <c r="E541" t="n">
         <v>0</v>
@@ -18885,17 +18873,17 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Farmana SO</t>
+          <t>Police Training Center Sunaria SO</t>
         </is>
       </c>
       <c r="B542" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C542" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D542" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E542" t="n">
         <v>0</v>
@@ -18919,14 +18907,14 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Gohana Mandi SO</t>
+          <t>Rohtak HO</t>
         </is>
       </c>
       <c r="B543" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C543" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D543" t="n">
         <v>5</v>
@@ -18935,10 +18923,10 @@
         <v>0</v>
       </c>
       <c r="F543" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G543" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -18953,17 +18941,17 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Gohana SO</t>
+          <t>Rohtak Sector I SO</t>
         </is>
       </c>
       <c r="B544" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C544" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D544" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E544" t="n">
         <v>0</v>
@@ -18987,17 +18975,17 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Kanyagurukul Khanpur SO</t>
+          <t>Rohtak Town SO</t>
         </is>
       </c>
       <c r="B545" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C545" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D545" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E545" t="n">
         <v>0</v>
@@ -19021,26 +19009,26 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Kharkhauda SO</t>
+          <t>Sanghi SO</t>
         </is>
       </c>
       <c r="B546" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C546" t="n">
         <v>2</v>
       </c>
       <c r="D546" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E546" t="n">
         <v>0</v>
       </c>
       <c r="F546" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G546" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -19055,7 +19043,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Mini Sectt Gohana</t>
+          <t>Shivaji Colony SO</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -19089,232 +19077,232 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Mundlana SO</t>
+          <t>Total:</t>
         </is>
       </c>
       <c r="B548" t="n">
-        <v>34</v>
+        <v>196</v>
       </c>
       <c r="C548" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="D548" t="n">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="E548" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F548" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G548" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
       </c>
       <c r="I548" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J548" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
-        <is>
-          <t>Purkhas SO</t>
-        </is>
-      </c>
-      <c r="B549" t="n">
-        <v>0</v>
-      </c>
-      <c r="C549" t="n">
-        <v>0</v>
-      </c>
-      <c r="D549" t="n">
-        <v>0</v>
-      </c>
-      <c r="E549" t="n">
-        <v>0</v>
-      </c>
-      <c r="F549" t="n">
-        <v>0</v>
-      </c>
-      <c r="G549" t="n">
-        <v>0</v>
-      </c>
-      <c r="H549" t="n">
-        <v>0</v>
-      </c>
-      <c r="I549" t="n">
-        <v>0</v>
-      </c>
-      <c r="J549" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>Sonipat HO</t>
-        </is>
-      </c>
-      <c r="B550" t="n">
-        <v>41</v>
-      </c>
-      <c r="C550" t="n">
-        <v>4</v>
-      </c>
-      <c r="D550" t="n">
-        <v>37</v>
-      </c>
-      <c r="E550" t="n">
-        <v>4</v>
-      </c>
-      <c r="F550" t="n">
-        <v>4</v>
-      </c>
-      <c r="G550" t="n">
-        <v>0</v>
-      </c>
-      <c r="H550" t="n">
-        <v>0</v>
-      </c>
-      <c r="I550" t="n">
-        <v>0</v>
-      </c>
-      <c r="J550" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>Total:</t>
-        </is>
-      </c>
-      <c r="B551" t="n">
-        <v>175</v>
-      </c>
-      <c r="C551" t="n">
-        <v>28</v>
-      </c>
-      <c r="D551" t="n">
-        <v>147</v>
-      </c>
-      <c r="E551" t="n">
-        <v>4</v>
-      </c>
-      <c r="F551" t="n">
-        <v>5</v>
-      </c>
-      <c r="G551" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H551" t="n">
-        <v>0</v>
-      </c>
-      <c r="I551" t="n">
-        <v>0</v>
-      </c>
-      <c r="J551" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Product Wise A/C Report
 </t>
         </is>
       </c>
-      <c r="B552" t="inlineStr"/>
-      <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr"/>
-      <c r="E552" t="inlineStr"/>
-      <c r="F552" t="inlineStr"/>
-      <c r="G552" t="inlineStr"/>
-      <c r="H552" t="inlineStr"/>
-      <c r="I552" t="inlineStr"/>
-      <c r="J552" t="inlineStr"/>
+      <c r="B549" t="inlineStr"/>
+      <c r="C549" t="inlineStr"/>
+      <c r="D549" t="inlineStr"/>
+      <c r="E549" t="inlineStr"/>
+      <c r="F549" t="inlineStr"/>
+      <c r="G549" t="inlineStr"/>
+      <c r="H549" t="inlineStr"/>
+      <c r="I549" t="inlineStr"/>
+      <c r="J549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>A/c Opened</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>A/c Closed</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Cert Issued</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Cert Discharged</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>A/c Opened</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>A/c Closed</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Baroda SO</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>0</v>
+      </c>
+      <c r="C551" t="n">
+        <v>1</v>
+      </c>
+      <c r="D551" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E551" t="n">
+        <v>0</v>
+      </c>
+      <c r="F551" t="n">
+        <v>0</v>
+      </c>
+      <c r="G551" t="n">
+        <v>0</v>
+      </c>
+      <c r="H551" t="n">
+        <v>0</v>
+      </c>
+      <c r="I551" t="n">
+        <v>0</v>
+      </c>
+      <c r="J551" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Bhainswal Kalan SO</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>0</v>
+      </c>
+      <c r="C552" t="n">
+        <v>1</v>
+      </c>
+      <c r="D552" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E552" t="n">
+        <v>0</v>
+      </c>
+      <c r="F552" t="n">
+        <v>0</v>
+      </c>
+      <c r="G552" t="n">
+        <v>0</v>
+      </c>
+      <c r="H552" t="n">
+        <v>0</v>
+      </c>
+      <c r="I552" t="n">
+        <v>0</v>
+      </c>
+      <c r="J552" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>A/c Opened</t>
-        </is>
-      </c>
-      <c r="C553" t="inlineStr">
-        <is>
-          <t>A/c Closed</t>
-        </is>
-      </c>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E553" t="inlineStr">
-        <is>
-          <t>Cert Issued</t>
-        </is>
-      </c>
-      <c r="F553" t="inlineStr">
-        <is>
-          <t>Cert Discharged</t>
-        </is>
-      </c>
-      <c r="G553" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="H553" t="inlineStr">
-        <is>
-          <t>A/c Opened</t>
-        </is>
-      </c>
-      <c r="I553" t="inlineStr">
-        <is>
-          <t>A/c Closed</t>
-        </is>
-      </c>
-      <c r="J553" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
+          <t>Bus Stand Gohana SO</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>0</v>
+      </c>
+      <c r="C553" t="n">
+        <v>0</v>
+      </c>
+      <c r="D553" t="n">
+        <v>0</v>
+      </c>
+      <c r="E553" t="n">
+        <v>0</v>
+      </c>
+      <c r="F553" t="n">
+        <v>0</v>
+      </c>
+      <c r="G553" t="n">
+        <v>0</v>
+      </c>
+      <c r="H553" t="n">
+        <v>0</v>
+      </c>
+      <c r="I553" t="n">
+        <v>0</v>
+      </c>
+      <c r="J553" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Atlas Cycle SO</t>
+          <t>Butana SO</t>
         </is>
       </c>
       <c r="B554" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C554" t="n">
         <v>2</v>
       </c>
       <c r="D554" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E554" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F554" t="n">
         <v>0</v>
       </c>
       <c r="G554" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -19329,17 +19317,17 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Bahalgarh SO</t>
+          <t>Farmana SO</t>
         </is>
       </c>
       <c r="B555" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C555" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D555" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E555" t="n">
         <v>0</v>
@@ -19363,17 +19351,17 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Bhatgaon SO Sonipat</t>
+          <t>Gohana Mandi SO</t>
         </is>
       </c>
       <c r="B556" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C556" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D556" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E556" t="n">
         <v>0</v>
@@ -19397,17 +19385,17 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Engg College Muthal SO</t>
+          <t>Gohana SO</t>
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C557" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D557" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E557" t="n">
         <v>0</v>
@@ -19431,14 +19419,14 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Ganaur City SO</t>
+          <t>Kanyagurukul Khanpur SO</t>
         </is>
       </c>
       <c r="B558" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C558" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D558" t="n">
         <v>3</v>
@@ -19465,26 +19453,26 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Ganaur SO</t>
+          <t>Kharkhauda SO</t>
         </is>
       </c>
       <c r="B559" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C559" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D559" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E559" t="n">
         <v>0</v>
       </c>
       <c r="F559" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G559" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H559" t="n">
         <v>0</v>
@@ -19499,7 +19487,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Ganzbazar SO</t>
+          <t>Mini Sectt Gohana</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -19533,17 +19521,17 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Gohana Road SO Sonipat</t>
+          <t>Mundlana SO</t>
         </is>
       </c>
       <c r="B561" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C561" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D561" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E561" t="n">
         <v>0</v>
@@ -19567,7 +19555,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>HOUSING BOARD COLONY SONIPAT</t>
+          <t>Purkhas SO</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -19583,10 +19571,10 @@
         <v>0</v>
       </c>
       <c r="F562" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G562" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -19601,23 +19589,23 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Industrial Estate Kundli SO</t>
+          <t>Sonipat HO</t>
         </is>
       </c>
       <c r="B563" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C563" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D563" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E563" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F563" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G563" t="n">
         <v>0</v>
@@ -19635,26 +19623,26 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Jakhauli SO</t>
+          <t>Total:</t>
         </is>
       </c>
       <c r="B564" t="n">
-        <v>1</v>
+        <v>175</v>
       </c>
       <c r="C564" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D564" t="n">
-        <v>1</v>
+        <v>147</v>
       </c>
       <c r="E564" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F564" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G564" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H564" t="n">
         <v>0</v>
@@ -19669,94 +19657,96 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Juan SO</t>
-        </is>
-      </c>
-      <c r="B565" t="n">
-        <v>17</v>
-      </c>
-      <c r="C565" t="n">
-        <v>4</v>
-      </c>
-      <c r="D565" t="n">
-        <v>13</v>
-      </c>
-      <c r="E565" t="n">
-        <v>0</v>
-      </c>
-      <c r="F565" t="n">
-        <v>0</v>
-      </c>
-      <c r="G565" t="n">
-        <v>0</v>
-      </c>
-      <c r="H565" t="n">
-        <v>0</v>
-      </c>
-      <c r="I565" t="n">
-        <v>0</v>
-      </c>
-      <c r="J565" t="n">
-        <v>0</v>
-      </c>
+          <t xml:space="preserve">
+Product Wise A/C Report
+</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr"/>
+      <c r="C565" t="inlineStr"/>
+      <c r="D565" t="inlineStr"/>
+      <c r="E565" t="inlineStr"/>
+      <c r="F565" t="inlineStr"/>
+      <c r="G565" t="inlineStr"/>
+      <c r="H565" t="inlineStr"/>
+      <c r="I565" t="inlineStr"/>
+      <c r="J565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Model Town Sonipat SO</t>
-        </is>
-      </c>
-      <c r="B566" t="n">
-        <v>0</v>
-      </c>
-      <c r="C566" t="n">
-        <v>0</v>
-      </c>
-      <c r="D566" t="n">
-        <v>0</v>
-      </c>
-      <c r="E566" t="n">
-        <v>0</v>
-      </c>
-      <c r="F566" t="n">
-        <v>0</v>
-      </c>
-      <c r="G566" t="n">
-        <v>0</v>
-      </c>
-      <c r="H566" t="n">
-        <v>0</v>
-      </c>
-      <c r="I566" t="n">
-        <v>0</v>
-      </c>
-      <c r="J566" t="n">
-        <v>0</v>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>A/c Opened</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>A/c Closed</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Cert Issued</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Cert Discharged</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>A/c Opened</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>A/c Closed</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Murthal SO</t>
+          <t>Atlas Cycle SO</t>
         </is>
       </c>
       <c r="B567" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C567" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D567" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E567" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F567" t="n">
         <v>0</v>
       </c>
       <c r="G567" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -19771,17 +19761,17 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Nahri SO</t>
+          <t>Bahalgarh SO</t>
         </is>
       </c>
       <c r="B568" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C568" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D568" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E568" t="n">
         <v>0</v>
@@ -19805,17 +19795,17 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>PSRai SO</t>
+          <t>Bhatgaon SO Sonipat</t>
         </is>
       </c>
       <c r="B569" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C569" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D569" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E569" t="n">
         <v>0</v>
@@ -19839,7 +19829,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Ram BazarSonipat SO</t>
+          <t>Engg College Muthal SO</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -19873,17 +19863,17 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Rathdhana Road Sonipat SO</t>
+          <t>Ganaur City SO</t>
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C571" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D571" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E571" t="n">
         <v>0</v>
@@ -19907,17 +19897,17 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Rohat SO Sonipat</t>
+          <t>Ganaur SO</t>
         </is>
       </c>
       <c r="B572" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C572" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D572" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E572" t="n">
         <v>0</v>
@@ -19941,17 +19931,17 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Sonipat Kty SO</t>
+          <t>Ganzbazar SO</t>
         </is>
       </c>
       <c r="B573" t="n">
         <v>0</v>
       </c>
       <c r="C573" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D573" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E573" t="n">
         <v>0</v>
@@ -19975,17 +19965,17 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Sonipat Mandi SO</t>
+          <t>Gohana Road SO Sonipat</t>
         </is>
       </c>
       <c r="B574" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C574" t="n">
         <v>1</v>
       </c>
       <c r="D574" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E574" t="n">
         <v>0</v>
@@ -20009,17 +19999,17 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Sonipat Sector 14 SO</t>
+          <t>HOUSING BOARD COLONY SONIPAT</t>
         </is>
       </c>
       <c r="B575" t="n">
         <v>0</v>
       </c>
       <c r="C575" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D575" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E575" t="n">
         <v>0</v>
@@ -20043,34 +20033,476 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
+          <t>Industrial Estate Kundli SO</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>31</v>
+      </c>
+      <c r="C576" t="n">
+        <v>0</v>
+      </c>
+      <c r="D576" t="n">
+        <v>31</v>
+      </c>
+      <c r="E576" t="n">
+        <v>0</v>
+      </c>
+      <c r="F576" t="n">
+        <v>0</v>
+      </c>
+      <c r="G576" t="n">
+        <v>0</v>
+      </c>
+      <c r="H576" t="n">
+        <v>0</v>
+      </c>
+      <c r="I576" t="n">
+        <v>0</v>
+      </c>
+      <c r="J576" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Jakhauli SO</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>1</v>
+      </c>
+      <c r="C577" t="n">
+        <v>0</v>
+      </c>
+      <c r="D577" t="n">
+        <v>1</v>
+      </c>
+      <c r="E577" t="n">
+        <v>0</v>
+      </c>
+      <c r="F577" t="n">
+        <v>0</v>
+      </c>
+      <c r="G577" t="n">
+        <v>0</v>
+      </c>
+      <c r="H577" t="n">
+        <v>0</v>
+      </c>
+      <c r="I577" t="n">
+        <v>0</v>
+      </c>
+      <c r="J577" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Juan SO</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>17</v>
+      </c>
+      <c r="C578" t="n">
+        <v>4</v>
+      </c>
+      <c r="D578" t="n">
+        <v>13</v>
+      </c>
+      <c r="E578" t="n">
+        <v>0</v>
+      </c>
+      <c r="F578" t="n">
+        <v>0</v>
+      </c>
+      <c r="G578" t="n">
+        <v>0</v>
+      </c>
+      <c r="H578" t="n">
+        <v>0</v>
+      </c>
+      <c r="I578" t="n">
+        <v>0</v>
+      </c>
+      <c r="J578" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Model Town Sonipat SO</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>0</v>
+      </c>
+      <c r="C579" t="n">
+        <v>0</v>
+      </c>
+      <c r="D579" t="n">
+        <v>0</v>
+      </c>
+      <c r="E579" t="n">
+        <v>0</v>
+      </c>
+      <c r="F579" t="n">
+        <v>0</v>
+      </c>
+      <c r="G579" t="n">
+        <v>0</v>
+      </c>
+      <c r="H579" t="n">
+        <v>0</v>
+      </c>
+      <c r="I579" t="n">
+        <v>0</v>
+      </c>
+      <c r="J579" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Murthal SO</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>4</v>
+      </c>
+      <c r="C580" t="n">
+        <v>1</v>
+      </c>
+      <c r="D580" t="n">
+        <v>3</v>
+      </c>
+      <c r="E580" t="n">
+        <v>0</v>
+      </c>
+      <c r="F580" t="n">
+        <v>0</v>
+      </c>
+      <c r="G580" t="n">
+        <v>0</v>
+      </c>
+      <c r="H580" t="n">
+        <v>0</v>
+      </c>
+      <c r="I580" t="n">
+        <v>0</v>
+      </c>
+      <c r="J580" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Nahri SO</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>2</v>
+      </c>
+      <c r="C581" t="n">
+        <v>0</v>
+      </c>
+      <c r="D581" t="n">
+        <v>2</v>
+      </c>
+      <c r="E581" t="n">
+        <v>0</v>
+      </c>
+      <c r="F581" t="n">
+        <v>0</v>
+      </c>
+      <c r="G581" t="n">
+        <v>0</v>
+      </c>
+      <c r="H581" t="n">
+        <v>0</v>
+      </c>
+      <c r="I581" t="n">
+        <v>0</v>
+      </c>
+      <c r="J581" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>PSRai SO</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>5</v>
+      </c>
+      <c r="C582" t="n">
+        <v>0</v>
+      </c>
+      <c r="D582" t="n">
+        <v>5</v>
+      </c>
+      <c r="E582" t="n">
+        <v>0</v>
+      </c>
+      <c r="F582" t="n">
+        <v>0</v>
+      </c>
+      <c r="G582" t="n">
+        <v>0</v>
+      </c>
+      <c r="H582" t="n">
+        <v>0</v>
+      </c>
+      <c r="I582" t="n">
+        <v>0</v>
+      </c>
+      <c r="J582" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Ram BazarSonipat SO</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>0</v>
+      </c>
+      <c r="C583" t="n">
+        <v>0</v>
+      </c>
+      <c r="D583" t="n">
+        <v>0</v>
+      </c>
+      <c r="E583" t="n">
+        <v>0</v>
+      </c>
+      <c r="F583" t="n">
+        <v>0</v>
+      </c>
+      <c r="G583" t="n">
+        <v>0</v>
+      </c>
+      <c r="H583" t="n">
+        <v>0</v>
+      </c>
+      <c r="I583" t="n">
+        <v>0</v>
+      </c>
+      <c r="J583" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Rathdhana Road Sonipat SO</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>0</v>
+      </c>
+      <c r="C584" t="n">
+        <v>0</v>
+      </c>
+      <c r="D584" t="n">
+        <v>0</v>
+      </c>
+      <c r="E584" t="n">
+        <v>0</v>
+      </c>
+      <c r="F584" t="n">
+        <v>0</v>
+      </c>
+      <c r="G584" t="n">
+        <v>0</v>
+      </c>
+      <c r="H584" t="n">
+        <v>0</v>
+      </c>
+      <c r="I584" t="n">
+        <v>0</v>
+      </c>
+      <c r="J584" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Rohat SO Sonipat</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>2</v>
+      </c>
+      <c r="C585" t="n">
+        <v>2</v>
+      </c>
+      <c r="D585" t="n">
+        <v>0</v>
+      </c>
+      <c r="E585" t="n">
+        <v>0</v>
+      </c>
+      <c r="F585" t="n">
+        <v>0</v>
+      </c>
+      <c r="G585" t="n">
+        <v>0</v>
+      </c>
+      <c r="H585" t="n">
+        <v>0</v>
+      </c>
+      <c r="I585" t="n">
+        <v>0</v>
+      </c>
+      <c r="J585" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Sonipat Kty SO</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>0</v>
+      </c>
+      <c r="C586" t="n">
+        <v>1</v>
+      </c>
+      <c r="D586" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E586" t="n">
+        <v>0</v>
+      </c>
+      <c r="F586" t="n">
+        <v>0</v>
+      </c>
+      <c r="G586" t="n">
+        <v>0</v>
+      </c>
+      <c r="H586" t="n">
+        <v>0</v>
+      </c>
+      <c r="I586" t="n">
+        <v>0</v>
+      </c>
+      <c r="J586" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Sonipat Mandi SO</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>3</v>
+      </c>
+      <c r="C587" t="n">
+        <v>1</v>
+      </c>
+      <c r="D587" t="n">
+        <v>2</v>
+      </c>
+      <c r="E587" t="n">
+        <v>0</v>
+      </c>
+      <c r="F587" t="n">
+        <v>0</v>
+      </c>
+      <c r="G587" t="n">
+        <v>0</v>
+      </c>
+      <c r="H587" t="n">
+        <v>0</v>
+      </c>
+      <c r="I587" t="n">
+        <v>0</v>
+      </c>
+      <c r="J587" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Sonipat Sector 14 SO</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>0</v>
+      </c>
+      <c r="C588" t="n">
+        <v>1</v>
+      </c>
+      <c r="D588" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E588" t="n">
+        <v>0</v>
+      </c>
+      <c r="F588" t="n">
+        <v>1</v>
+      </c>
+      <c r="G588" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H588" t="n">
+        <v>0</v>
+      </c>
+      <c r="I588" t="n">
+        <v>0</v>
+      </c>
+      <c r="J588" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
           <t>Total:</t>
         </is>
       </c>
-      <c r="B576" t="n">
+      <c r="B589" t="n">
         <v>104</v>
       </c>
-      <c r="C576" t="n">
+      <c r="C589" t="n">
         <v>26</v>
       </c>
-      <c r="D576" t="n">
+      <c r="D589" t="n">
         <v>78</v>
       </c>
-      <c r="E576" t="n">
-        <v>1</v>
-      </c>
-      <c r="F576" t="n">
+      <c r="E589" t="n">
+        <v>1</v>
+      </c>
+      <c r="F589" t="n">
         <v>2</v>
       </c>
-      <c r="G576" t="n">
+      <c r="G589" t="n">
         <v>-1</v>
       </c>
-      <c r="H576" t="n">
-        <v>0</v>
-      </c>
-      <c r="I576" t="n">
-        <v>0</v>
-      </c>
-      <c r="J576" t="n">
+      <c r="H589" t="n">
+        <v>0</v>
+      </c>
+      <c r="I589" t="n">
+        <v>0</v>
+      </c>
+      <c r="J589" t="n">
         <v>0</v>
       </c>
     </row>
